--- a/审核导出/silicone_coarse_uv_审核.xlsx
+++ b/审核导出/silicone_coarse_uv_审核.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>第二加工工藝「絲印巖石UV」專用。 / 物料經絲印於紙張上，其涂層具有獨特的立體粗糙磨砂手感效果。</t>
+          <t>第二加工工藝「絲印巖石UV」專用。 / 物料經絲印於紙張上，其塗層具有獨特的立體粗糙磨砂手感效果。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -748,12 +748,12 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
